--- a/NBS FINAL delivery/03_Excel_Deliveries/8_Artist_Population_Frame.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/8_Artist_Population_Frame.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T20:13:47.903954+00:00</t>
+          <t>2026-08-31T23:48:51.976270+00:00</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
         <v>31</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>42960525.64</v>
+        <v>42960525.66</v>
       </c>
     </row>
     <row r="3">
@@ -649,7 +649,7 @@
         <v>31</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>37196147.88</v>
+        <v>37196147.87</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
         <v>31</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>16202945.28</v>
+        <v>16202945.29</v>
       </c>
     </row>
     <row r="10">
@@ -913,7 +913,7 @@
         <v>31</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>14835906.76</v>
+        <v>14835906.78</v>
       </c>
     </row>
     <row r="12">
@@ -946,7 +946,7 @@
         <v>31</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>14554700.62</v>
+        <v>14554700.63</v>
       </c>
     </row>
     <row r="13">
@@ -979,7 +979,7 @@
         <v>31</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>10816064.97</v>
+        <v>10816064.94</v>
       </c>
     </row>
     <row r="14">
@@ -1078,7 +1078,7 @@
         <v>31</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>10114272.17</v>
+        <v>10114272.18</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>31</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>8484168.210000001</v>
+        <v>8484168.189999999</v>
       </c>
     </row>
     <row r="18">
@@ -1210,7 +1210,7 @@
         <v>31</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>7216616.44</v>
+        <v>7216616.45</v>
       </c>
     </row>
     <row r="21">
@@ -1243,7 +1243,7 @@
         <v>31</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>6823995.85</v>
+        <v>6823995.87</v>
       </c>
     </row>
     <row r="22">
@@ -1342,7 +1342,7 @@
         <v>31</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>6521729.28</v>
+        <v>6521729.3</v>
       </c>
     </row>
     <row r="25">
@@ -1474,7 +1474,7 @@
         <v>31</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>5779856.55</v>
+        <v>5779856.56</v>
       </c>
     </row>
     <row r="29">
@@ -1573,7 +1573,7 @@
         <v>31</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>5279335.28</v>
+        <v>5279335.26</v>
       </c>
     </row>
     <row r="32">
@@ -1639,7 +1639,7 @@
         <v>31</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4919045.45</v>
+        <v>4919045.44</v>
       </c>
     </row>
     <row r="34">
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>4453253.35</v>
+        <v>4453253.37</v>
       </c>
     </row>
     <row r="35">
@@ -1738,7 +1738,7 @@
         <v>31</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>4414442.89</v>
+        <v>4414442.9</v>
       </c>
     </row>
     <row r="37">
@@ -1771,7 +1771,7 @@
         <v>31</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>4165320.24</v>
+        <v>4165320.26</v>
       </c>
     </row>
     <row r="38">
@@ -1804,7 +1804,7 @@
         <v>31</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>4162272.24</v>
+        <v>4162272.23</v>
       </c>
     </row>
     <row r="39">
@@ -1870,7 +1870,7 @@
         <v>31</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>3793394.22</v>
+        <v>3793394.2</v>
       </c>
     </row>
     <row r="41">
@@ -2068,7 +2068,7 @@
         <v>31</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>3327631.91</v>
+        <v>3327631.92</v>
       </c>
     </row>
     <row r="47">
@@ -2233,7 +2233,7 @@
         <v>31</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>3178110.9</v>
+        <v>3178110.92</v>
       </c>
     </row>
     <row r="52">
@@ -2299,7 +2299,7 @@
         <v>31</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3049494.19</v>
+        <v>3049494.18</v>
       </c>
     </row>
     <row r="54">
@@ -2332,7 +2332,7 @@
         <v>31</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>3018136.9</v>
+        <v>3018136.92</v>
       </c>
     </row>
     <row r="55">
@@ -2596,7 +2596,7 @@
         <v>31</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>2646094.82</v>
+        <v>2646094.84</v>
       </c>
     </row>
     <row r="63">
@@ -2662,7 +2662,7 @@
         <v>31</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>2472020.95</v>
+        <v>2472020.96</v>
       </c>
     </row>
     <row r="65">
@@ -2695,7 +2695,7 @@
         <v>31</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>2402569.32</v>
+        <v>2402569.3</v>
       </c>
     </row>
     <row r="66">
@@ -2761,7 +2761,7 @@
         <v>31</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>2263306.34</v>
+        <v>2263306.35</v>
       </c>
     </row>
     <row r="68">
@@ -2860,7 +2860,7 @@
         <v>31</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>2181993.42</v>
+        <v>2181993.44</v>
       </c>
     </row>
     <row r="71">
@@ -2893,7 +2893,7 @@
         <v>31</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>2153761.71</v>
+        <v>2153761.7</v>
       </c>
     </row>
     <row r="72">
@@ -2959,7 +2959,7 @@
         <v>31</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>2124191.36</v>
+        <v>2124191.38</v>
       </c>
     </row>
     <row r="74">
@@ -3058,7 +3058,7 @@
         <v>31</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>1985119.59</v>
+        <v>1985119.58</v>
       </c>
     </row>
     <row r="77">
@@ -3091,7 +3091,7 @@
         <v>31</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>1921433.25</v>
+        <v>1921433.22</v>
       </c>
     </row>
     <row r="78">
@@ -3124,7 +3124,7 @@
         <v>31</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>1893076.39</v>
+        <v>1893076.41</v>
       </c>
     </row>
     <row r="79">
@@ -3223,7 +3223,7 @@
         <v>31</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>1818912.79</v>
+        <v>1818912.78</v>
       </c>
     </row>
     <row r="82">
@@ -3256,7 +3256,7 @@
         <v>31</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>1815324.49</v>
+        <v>1815324.46</v>
       </c>
     </row>
     <row r="83">
@@ -3322,7 +3322,7 @@
         <v>31</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>1703342.22</v>
+        <v>1703342.19</v>
       </c>
     </row>
     <row r="85">
@@ -3355,7 +3355,7 @@
         <v>31</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>1682344.35</v>
+        <v>1682344.34</v>
       </c>
     </row>
     <row r="86">
@@ -3421,7 +3421,7 @@
         <v>31</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>1601003.77</v>
+        <v>1601003.79</v>
       </c>
     </row>
     <row r="88">
@@ -3454,7 +3454,7 @@
         <v>31</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>1584852.16</v>
+        <v>1584852.14</v>
       </c>
     </row>
     <row r="89">
@@ -3487,7 +3487,7 @@
         <v>31</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>1571391.79</v>
+        <v>1571391.76</v>
       </c>
     </row>
     <row r="90">
@@ -3520,7 +3520,7 @@
         <v>31</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>1535144.71</v>
+        <v>1535144.68</v>
       </c>
     </row>
     <row r="91">
@@ -3586,7 +3586,7 @@
         <v>31</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>1488874.03</v>
+        <v>1488874</v>
       </c>
     </row>
     <row r="93">
@@ -3718,7 +3718,7 @@
         <v>31</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>1374229.6</v>
+        <v>1374229.58</v>
       </c>
     </row>
     <row r="97">
@@ -3751,7 +3751,7 @@
         <v>31</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>1358334.53</v>
+        <v>1358334.52</v>
       </c>
     </row>
     <row r="98">
@@ -3784,7 +3784,7 @@
         <v>31</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>1330805.6</v>
+        <v>1330805.62</v>
       </c>
     </row>
     <row r="99">
@@ -3916,7 +3916,7 @@
         <v>31</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>1216792.18</v>
+        <v>1216792.2</v>
       </c>
     </row>
     <row r="103">
@@ -3982,7 +3982,7 @@
         <v>31</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>1183381.42</v>
+        <v>1183381.41</v>
       </c>
     </row>
     <row r="105">
@@ -4114,7 +4114,7 @@
         <v>31</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>1137291.54</v>
+        <v>1137291.55</v>
       </c>
     </row>
     <row r="109">
@@ -4147,7 +4147,7 @@
         <v>31</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>1117489.85</v>
+        <v>1117489.87</v>
       </c>
     </row>
     <row r="110">
@@ -4213,7 +4213,7 @@
         <v>31</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>1114905.96</v>
+        <v>1114905.95</v>
       </c>
     </row>
     <row r="112">
@@ -4246,7 +4246,7 @@
         <v>31</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>1109651.4</v>
+        <v>1109651.41</v>
       </c>
     </row>
     <row r="113">
@@ -4411,7 +4411,7 @@
         <v>31</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>1007699.69</v>
+        <v>1007699.7</v>
       </c>
     </row>
     <row r="118">
@@ -4444,7 +4444,7 @@
         <v>31</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>1006403.46</v>
+        <v>1006403.44</v>
       </c>
     </row>
     <row r="119">
@@ -4576,7 +4576,7 @@
         <v>31</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>962735.47</v>
+        <v>962735.45</v>
       </c>
     </row>
     <row r="123">
@@ -4675,7 +4675,7 @@
         <v>31</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>935501.46</v>
+        <v>935501.45</v>
       </c>
     </row>
     <row r="126">
@@ -4741,7 +4741,7 @@
         <v>31</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>906627.51</v>
+        <v>906627.49</v>
       </c>
     </row>
     <row r="128">
@@ -4873,7 +4873,7 @@
         <v>31</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>878797.24</v>
+        <v>878797.25</v>
       </c>
     </row>
     <row r="132">
@@ -4906,7 +4906,7 @@
         <v>31</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>878405.72</v>
+        <v>878405.73</v>
       </c>
     </row>
     <row r="133">
@@ -5067,7 +5067,7 @@
         <v>31</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>798805.04</v>
+        <v>798805.0699999999</v>
       </c>
     </row>
     <row r="138">
@@ -5199,7 +5199,7 @@
         <v>31</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>751822.71</v>
+        <v>751822.6800000001</v>
       </c>
     </row>
     <row r="142">
@@ -5232,7 +5232,7 @@
         <v>31</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>747696.28</v>
+        <v>747696.26</v>
       </c>
     </row>
     <row r="143">
@@ -5661,7 +5661,7 @@
         <v>31</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>649317.09</v>
+        <v>649317.0600000001</v>
       </c>
     </row>
     <row r="156">
@@ -5793,7 +5793,7 @@
         <v>31</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>626212.98</v>
+        <v>626213</v>
       </c>
     </row>
     <row r="160">
@@ -5892,7 +5892,7 @@
         <v>31</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>607756.74</v>
+        <v>607756.77</v>
       </c>
     </row>
     <row r="163">
@@ -5925,7 +5925,7 @@
         <v>31</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>604469.84</v>
+        <v>604469.85</v>
       </c>
     </row>
     <row r="164">
@@ -5958,7 +5958,7 @@
         <v>31</v>
       </c>
       <c r="G164" s="7" t="n">
-        <v>600116.8100000001</v>
+        <v>600116.8199999999</v>
       </c>
     </row>
     <row r="165">
@@ -6057,7 +6057,7 @@
         <v>31</v>
       </c>
       <c r="G167" s="7" t="n">
-        <v>587946.03</v>
+        <v>587946.01</v>
       </c>
     </row>
     <row r="168">
@@ -6123,7 +6123,7 @@
         <v>31</v>
       </c>
       <c r="G169" s="7" t="n">
-        <v>582966.0600000001</v>
+        <v>582966.0699999999</v>
       </c>
     </row>
     <row r="170">
@@ -6156,7 +6156,7 @@
         <v>31</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>579144.01</v>
+        <v>579144.02</v>
       </c>
     </row>
     <row r="171">
@@ -6321,7 +6321,7 @@
         <v>31</v>
       </c>
       <c r="G175" s="7" t="n">
-        <v>546557.51</v>
+        <v>546557.53</v>
       </c>
     </row>
     <row r="176">
@@ -6453,7 +6453,7 @@
         <v>31</v>
       </c>
       <c r="G179" s="7" t="n">
-        <v>535955.65</v>
+        <v>535955.66</v>
       </c>
     </row>
     <row r="180">
@@ -6618,7 +6618,7 @@
         <v>31</v>
       </c>
       <c r="G184" s="7" t="n">
-        <v>514581.19</v>
+        <v>514581.21</v>
       </c>
     </row>
     <row r="185">
@@ -6717,7 +6717,7 @@
         <v>31</v>
       </c>
       <c r="G187" s="7" t="n">
-        <v>504831.8</v>
+        <v>504831.79</v>
       </c>
     </row>
     <row r="188">
@@ -6750,7 +6750,7 @@
         <v>31</v>
       </c>
       <c r="G188" s="7" t="n">
-        <v>502372.91</v>
+        <v>502372.9</v>
       </c>
     </row>
     <row r="189">
@@ -6783,7 +6783,7 @@
         <v>31</v>
       </c>
       <c r="G189" s="7" t="n">
-        <v>498638.06</v>
+        <v>498638.05</v>
       </c>
     </row>
     <row r="190">
@@ -6816,7 +6816,7 @@
         <v>31</v>
       </c>
       <c r="G190" s="7" t="n">
-        <v>490667.86</v>
+        <v>490667.88</v>
       </c>
     </row>
     <row r="191">
@@ -6981,7 +6981,7 @@
         <v>31</v>
       </c>
       <c r="G195" s="7" t="n">
-        <v>459319.72</v>
+        <v>459319.71</v>
       </c>
     </row>
     <row r="196">
@@ -7014,7 +7014,7 @@
         <v>31</v>
       </c>
       <c r="G196" s="7" t="n">
-        <v>443054.17</v>
+        <v>443054.19</v>
       </c>
     </row>
     <row r="197">
@@ -7047,7 +7047,7 @@
         <v>31</v>
       </c>
       <c r="G197" s="7" t="n">
-        <v>438331.47</v>
+        <v>438331.44</v>
       </c>
     </row>
     <row r="198">
@@ -7080,7 +7080,7 @@
         <v>31</v>
       </c>
       <c r="G198" s="7" t="n">
-        <v>435677.21</v>
+        <v>435677.2</v>
       </c>
     </row>
     <row r="199">
@@ -7113,7 +7113,7 @@
         <v>31</v>
       </c>
       <c r="G199" s="7" t="n">
-        <v>425474.97</v>
+        <v>425474.98</v>
       </c>
     </row>
     <row r="200">
@@ -7146,7 +7146,7 @@
         <v>31</v>
       </c>
       <c r="G200" s="7" t="n">
-        <v>420585.22</v>
+        <v>420585.23</v>
       </c>
     </row>
     <row r="201">
@@ -7179,7 +7179,7 @@
         <v>31</v>
       </c>
       <c r="G201" s="7" t="n">
-        <v>417153.7</v>
+        <v>417153.71</v>
       </c>
     </row>
     <row r="202">
@@ -7212,7 +7212,7 @@
         <v>31</v>
       </c>
       <c r="G202" s="7" t="n">
-        <v>414204.38</v>
+        <v>414204.4</v>
       </c>
     </row>
     <row r="203">
@@ -7278,7 +7278,7 @@
         <v>31</v>
       </c>
       <c r="G204" s="7" t="n">
-        <v>397198.51</v>
+        <v>397198.5</v>
       </c>
     </row>
     <row r="205">
@@ -7311,7 +7311,7 @@
         <v>31</v>
       </c>
       <c r="G205" s="7" t="n">
-        <v>397185.69</v>
+        <v>397185.71</v>
       </c>
     </row>
     <row r="206">
@@ -7344,7 +7344,7 @@
         <v>31</v>
       </c>
       <c r="G206" s="7" t="n">
-        <v>394456.64</v>
+        <v>394456.63</v>
       </c>
     </row>
     <row r="207">
@@ -7410,7 +7410,7 @@
         <v>31</v>
       </c>
       <c r="G208" s="7" t="n">
-        <v>389248.23</v>
+        <v>389248.22</v>
       </c>
     </row>
     <row r="209">
@@ -7509,7 +7509,7 @@
         <v>31</v>
       </c>
       <c r="G211" s="7" t="n">
-        <v>371057.64</v>
+        <v>371057.66</v>
       </c>
     </row>
     <row r="212">
@@ -7542,7 +7542,7 @@
         <v>31</v>
       </c>
       <c r="G212" s="7" t="n">
-        <v>370820.28</v>
+        <v>370820.3</v>
       </c>
     </row>
     <row r="213">
@@ -7806,7 +7806,7 @@
         <v>31</v>
       </c>
       <c r="G220" s="7" t="n">
-        <v>334402.08</v>
+        <v>334402.1</v>
       </c>
     </row>
     <row r="221">
@@ -7839,7 +7839,7 @@
         <v>31</v>
       </c>
       <c r="G221" s="7" t="n">
-        <v>333121.52</v>
+        <v>333121.53</v>
       </c>
     </row>
     <row r="222">
@@ -7905,7 +7905,7 @@
         <v>31</v>
       </c>
       <c r="G223" s="7" t="n">
-        <v>329729.41</v>
+        <v>329729.43</v>
       </c>
     </row>
     <row r="224">
@@ -8235,7 +8235,7 @@
         <v>31</v>
       </c>
       <c r="G233" s="7" t="n">
-        <v>308394.11</v>
+        <v>308394.13</v>
       </c>
     </row>
     <row r="234">
@@ -8301,7 +8301,7 @@
         <v>31</v>
       </c>
       <c r="G235" s="7" t="n">
-        <v>302711.15</v>
+        <v>302711.13</v>
       </c>
     </row>
     <row r="236">
@@ -8334,7 +8334,7 @@
         <v>31</v>
       </c>
       <c r="G236" s="7" t="n">
-        <v>299411.03</v>
+        <v>299411.05</v>
       </c>
     </row>
     <row r="237">
@@ -8367,7 +8367,7 @@
         <v>31</v>
       </c>
       <c r="G237" s="7" t="n">
-        <v>295198.37</v>
+        <v>295198.38</v>
       </c>
     </row>
     <row r="238">
@@ -8400,7 +8400,7 @@
         <v>31</v>
       </c>
       <c r="G238" s="7" t="n">
-        <v>294222.45</v>
+        <v>294222.46</v>
       </c>
     </row>
     <row r="239">
@@ -8532,7 +8532,7 @@
         <v>31</v>
       </c>
       <c r="G242" s="7" t="n">
-        <v>286862.94</v>
+        <v>286862.92</v>
       </c>
     </row>
     <row r="243">
@@ -8598,7 +8598,7 @@
         <v>31</v>
       </c>
       <c r="G244" s="7" t="n">
-        <v>279692.17</v>
+        <v>279692.15</v>
       </c>
     </row>
     <row r="245">
@@ -8631,7 +8631,7 @@
         <v>31</v>
       </c>
       <c r="G245" s="7" t="n">
-        <v>278766.04</v>
+        <v>278766.02</v>
       </c>
     </row>
     <row r="246">
@@ -8763,7 +8763,7 @@
         <v>31</v>
       </c>
       <c r="G249" s="7" t="n">
-        <v>270897.54</v>
+        <v>270897.55</v>
       </c>
     </row>
     <row r="250">
@@ -9027,7 +9027,7 @@
         <v>31</v>
       </c>
       <c r="G257" s="7" t="n">
-        <v>253782.66</v>
+        <v>253782.64</v>
       </c>
     </row>
     <row r="258">
@@ -9093,7 +9093,7 @@
         <v>31</v>
       </c>
       <c r="G259" s="7" t="n">
-        <v>249395.56</v>
+        <v>249395.57</v>
       </c>
     </row>
     <row r="260">
@@ -9159,7 +9159,7 @@
         <v>31</v>
       </c>
       <c r="G261" s="7" t="n">
-        <v>240796.32</v>
+        <v>240796.29</v>
       </c>
     </row>
     <row r="262">
@@ -9225,7 +9225,7 @@
         <v>31</v>
       </c>
       <c r="G263" s="7" t="n">
-        <v>238796.39</v>
+        <v>238796.4</v>
       </c>
     </row>
     <row r="264">
@@ -9258,7 +9258,7 @@
         <v>31</v>
       </c>
       <c r="G264" s="7" t="n">
-        <v>235517.58</v>
+        <v>235517.56</v>
       </c>
     </row>
     <row r="265">
@@ -9357,7 +9357,7 @@
         <v>31</v>
       </c>
       <c r="G267" s="7" t="n">
-        <v>232839.99</v>
+        <v>232840.02</v>
       </c>
     </row>
     <row r="268">
@@ -9390,7 +9390,7 @@
         <v>31</v>
       </c>
       <c r="G268" s="7" t="n">
-        <v>232600.67</v>
+        <v>232600.69</v>
       </c>
     </row>
     <row r="269">
@@ -9489,7 +9489,7 @@
         <v>31</v>
       </c>
       <c r="G271" s="7" t="n">
-        <v>228901.74</v>
+        <v>228901.76</v>
       </c>
     </row>
     <row r="272">
@@ -9621,7 +9621,7 @@
         <v>31</v>
       </c>
       <c r="G275" s="7" t="n">
-        <v>222172.49</v>
+        <v>222172.5</v>
       </c>
     </row>
     <row r="276">
@@ -9654,7 +9654,7 @@
         <v>31</v>
       </c>
       <c r="G276" s="7" t="n">
-        <v>217986.17</v>
+        <v>217986.15</v>
       </c>
     </row>
     <row r="277">
@@ -9720,7 +9720,7 @@
         <v>31</v>
       </c>
       <c r="G278" s="7" t="n">
-        <v>214825.46</v>
+        <v>214825.48</v>
       </c>
     </row>
     <row r="279">
@@ -9918,7 +9918,7 @@
         <v>31</v>
       </c>
       <c r="G284" s="7" t="n">
-        <v>197287.64</v>
+        <v>197287.63</v>
       </c>
     </row>
     <row r="285">
@@ -9984,7 +9984,7 @@
         <v>31</v>
       </c>
       <c r="G286" s="7" t="n">
-        <v>191448.81</v>
+        <v>191448.79</v>
       </c>
     </row>
     <row r="287">
@@ -10050,7 +10050,7 @@
         <v>31</v>
       </c>
       <c r="G288" s="7" t="n">
-        <v>188561.74</v>
+        <v>188561.73</v>
       </c>
     </row>
     <row r="289">
@@ -10079,7 +10079,7 @@
         <v>31</v>
       </c>
       <c r="G289" s="7" t="n">
-        <v>186483.41</v>
+        <v>186483.44</v>
       </c>
     </row>
     <row r="290">
@@ -10145,7 +10145,7 @@
         <v>31</v>
       </c>
       <c r="G291" s="7" t="n">
-        <v>183193.23</v>
+        <v>183193.25</v>
       </c>
     </row>
     <row r="292">
@@ -10178,7 +10178,7 @@
         <v>31</v>
       </c>
       <c r="G292" s="7" t="n">
-        <v>181556.85</v>
+        <v>181556.83</v>
       </c>
     </row>
     <row r="293">
@@ -10211,7 +10211,7 @@
         <v>31</v>
       </c>
       <c r="G293" s="7" t="n">
-        <v>174555.14</v>
+        <v>174555.16</v>
       </c>
     </row>
     <row r="294">
@@ -10244,7 +10244,7 @@
         <v>31</v>
       </c>
       <c r="G294" s="7" t="n">
-        <v>174405.69</v>
+        <v>174405.72</v>
       </c>
     </row>
     <row r="295">
@@ -10508,7 +10508,7 @@
         <v>31</v>
       </c>
       <c r="G302" s="7" t="n">
-        <v>162944.65</v>
+        <v>162944.62</v>
       </c>
     </row>
     <row r="303">
@@ -10541,7 +10541,7 @@
         <v>31</v>
       </c>
       <c r="G303" s="7" t="n">
-        <v>160713.62</v>
+        <v>160713.63</v>
       </c>
     </row>
     <row r="304">
@@ -10673,7 +10673,7 @@
         <v>31</v>
       </c>
       <c r="G307" s="7" t="n">
-        <v>153270.95</v>
+        <v>153270.98</v>
       </c>
     </row>
     <row r="308">
@@ -10739,7 +10739,7 @@
         <v>31</v>
       </c>
       <c r="G309" s="7" t="n">
-        <v>152150.27</v>
+        <v>152150.26</v>
       </c>
     </row>
     <row r="310">
@@ -10805,7 +10805,7 @@
         <v>31</v>
       </c>
       <c r="G311" s="7" t="n">
-        <v>148429.23</v>
+        <v>148429.24</v>
       </c>
     </row>
     <row r="312">
@@ -10838,7 +10838,7 @@
         <v>31</v>
       </c>
       <c r="G312" s="7" t="n">
-        <v>147783.49</v>
+        <v>147783.51</v>
       </c>
     </row>
     <row r="313">
@@ -10871,7 +10871,7 @@
         <v>31</v>
       </c>
       <c r="G313" s="7" t="n">
-        <v>147406.31</v>
+        <v>147406.29</v>
       </c>
     </row>
     <row r="314">
@@ -10937,7 +10937,7 @@
         <v>31</v>
       </c>
       <c r="G315" s="7" t="n">
-        <v>145903.66</v>
+        <v>145903.67</v>
       </c>
     </row>
     <row r="316">
@@ -11135,7 +11135,7 @@
         <v>31</v>
       </c>
       <c r="G321" s="7" t="n">
-        <v>136327.4</v>
+        <v>136327.41</v>
       </c>
     </row>
     <row r="322">
@@ -11201,7 +11201,7 @@
         <v>31</v>
       </c>
       <c r="G323" s="7" t="n">
-        <v>133539.86</v>
+        <v>133539.84</v>
       </c>
     </row>
     <row r="324">
@@ -11300,7 +11300,7 @@
         <v>31</v>
       </c>
       <c r="G326" s="7" t="n">
-        <v>131073.8</v>
+        <v>131073.78</v>
       </c>
     </row>
     <row r="327">
@@ -11366,7 +11366,7 @@
         <v>31</v>
       </c>
       <c r="G328" s="7" t="n">
-        <v>129640.87</v>
+        <v>129640.84</v>
       </c>
     </row>
     <row r="329">
@@ -11564,7 +11564,7 @@
         <v>31</v>
       </c>
       <c r="G334" s="7" t="n">
-        <v>119454.18</v>
+        <v>119454.16</v>
       </c>
     </row>
     <row r="335">
@@ -11630,7 +11630,7 @@
         <v>31</v>
       </c>
       <c r="G336" s="7" t="n">
-        <v>116450.1</v>
+        <v>116450.07</v>
       </c>
     </row>
     <row r="337">
@@ -11729,7 +11729,7 @@
         <v>31</v>
       </c>
       <c r="G339" s="7" t="n">
-        <v>113196.25</v>
+        <v>113196.26</v>
       </c>
     </row>
     <row r="340">
@@ -12026,7 +12026,7 @@
         <v>31</v>
       </c>
       <c r="G348" s="7" t="n">
-        <v>101706.08</v>
+        <v>101706.09</v>
       </c>
     </row>
     <row r="349">
@@ -12187,7 +12187,7 @@
         <v>31</v>
       </c>
       <c r="G353" s="7" t="n">
-        <v>96818.11</v>
+        <v>96818.08</v>
       </c>
     </row>
     <row r="354">
@@ -12220,7 +12220,7 @@
         <v>31</v>
       </c>
       <c r="G354" s="7" t="n">
-        <v>94672.46000000001</v>
+        <v>94672.48</v>
       </c>
     </row>
     <row r="355">
@@ -12286,7 +12286,7 @@
         <v>31</v>
       </c>
       <c r="G356" s="7" t="n">
-        <v>93322.38</v>
+        <v>93322.39</v>
       </c>
     </row>
     <row r="357">
@@ -12385,7 +12385,7 @@
         <v>31</v>
       </c>
       <c r="G359" s="7" t="n">
-        <v>89443.81</v>
+        <v>89443.83</v>
       </c>
     </row>
     <row r="360">
@@ -12451,7 +12451,7 @@
         <v>31</v>
       </c>
       <c r="G361" s="7" t="n">
-        <v>89174.19</v>
+        <v>89174.2</v>
       </c>
     </row>
     <row r="362">
@@ -12517,7 +12517,7 @@
         <v>31</v>
       </c>
       <c r="G363" s="7" t="n">
-        <v>86168.38</v>
+        <v>86168.39</v>
       </c>
     </row>
     <row r="364">
@@ -12583,7 +12583,7 @@
         <v>31</v>
       </c>
       <c r="G365" s="7" t="n">
-        <v>85600.75</v>
+        <v>85600.75999999999</v>
       </c>
     </row>
     <row r="366">
@@ -12616,7 +12616,7 @@
         <v>31</v>
       </c>
       <c r="G366" s="7" t="n">
-        <v>85524.42</v>
+        <v>85524.44</v>
       </c>
     </row>
     <row r="367">
@@ -12682,7 +12682,7 @@
         <v>31</v>
       </c>
       <c r="G368" s="7" t="n">
-        <v>84277.5</v>
+        <v>84277.50999999999</v>
       </c>
     </row>
     <row r="369">
@@ -12748,7 +12748,7 @@
         <v>31</v>
       </c>
       <c r="G370" s="7" t="n">
-        <v>84223.45</v>
+        <v>84223.47</v>
       </c>
     </row>
     <row r="371">
@@ -12847,7 +12847,7 @@
         <v>31</v>
       </c>
       <c r="G373" s="7" t="n">
-        <v>83713.61</v>
+        <v>83713.59</v>
       </c>
     </row>
     <row r="374">
@@ -13177,7 +13177,7 @@
         <v>31</v>
       </c>
       <c r="G383" s="7" t="n">
-        <v>78149.46000000001</v>
+        <v>78149.48</v>
       </c>
     </row>
     <row r="384">
@@ -13305,7 +13305,7 @@
         <v>31</v>
       </c>
       <c r="G387" s="7" t="n">
-        <v>73946.07000000001</v>
+        <v>73946.08</v>
       </c>
     </row>
     <row r="388">
@@ -13371,7 +13371,7 @@
         <v>31</v>
       </c>
       <c r="G389" s="7" t="n">
-        <v>71363.21000000001</v>
+        <v>71363.2</v>
       </c>
     </row>
     <row r="390">
@@ -13437,7 +13437,7 @@
         <v>31</v>
       </c>
       <c r="G391" s="7" t="n">
-        <v>70301.61</v>
+        <v>70301.59</v>
       </c>
     </row>
     <row r="392">
@@ -13470,7 +13470,7 @@
         <v>31</v>
       </c>
       <c r="G392" s="7" t="n">
-        <v>70116</v>
+        <v>70116.02</v>
       </c>
     </row>
     <row r="393">
@@ -13503,7 +13503,7 @@
         <v>31</v>
       </c>
       <c r="G393" s="7" t="n">
-        <v>69844.11</v>
+        <v>69844.13</v>
       </c>
     </row>
     <row r="394">
@@ -13635,7 +13635,7 @@
         <v>31</v>
       </c>
       <c r="G397" s="7" t="n">
-        <v>64956.09</v>
+        <v>64956.08</v>
       </c>
     </row>
     <row r="398">
@@ -13701,7 +13701,7 @@
         <v>31</v>
       </c>
       <c r="G399" s="7" t="n">
-        <v>64307.26</v>
+        <v>64307.24</v>
       </c>
     </row>
     <row r="400">
@@ -13899,7 +13899,7 @@
         <v>31</v>
       </c>
       <c r="G405" s="7" t="n">
-        <v>58766.47</v>
+        <v>58766.45</v>
       </c>
     </row>
     <row r="406">
@@ -13932,7 +13932,7 @@
         <v>31</v>
       </c>
       <c r="G406" s="7" t="n">
-        <v>58046.68</v>
+        <v>58046.65</v>
       </c>
     </row>
     <row r="407">
@@ -13965,7 +13965,7 @@
         <v>31</v>
       </c>
       <c r="G407" s="7" t="n">
-        <v>57862.23</v>
+        <v>57862.25</v>
       </c>
     </row>
     <row r="408">
@@ -14097,7 +14097,7 @@
         <v>31</v>
       </c>
       <c r="G411" s="7" t="n">
-        <v>54607.03</v>
+        <v>54607.01</v>
       </c>
     </row>
     <row r="412">
@@ -14196,7 +14196,7 @@
         <v>31</v>
       </c>
       <c r="G414" s="7" t="n">
-        <v>53988.76</v>
+        <v>53988.79</v>
       </c>
     </row>
     <row r="415">
@@ -14295,7 +14295,7 @@
         <v>31</v>
       </c>
       <c r="G417" s="7" t="n">
-        <v>53013.23</v>
+        <v>53013.25</v>
       </c>
     </row>
     <row r="418">
@@ -14361,7 +14361,7 @@
         <v>31</v>
       </c>
       <c r="G419" s="7" t="n">
-        <v>49488.23</v>
+        <v>49488.24</v>
       </c>
     </row>
     <row r="420">
@@ -14460,7 +14460,7 @@
         <v>31</v>
       </c>
       <c r="G422" s="7" t="n">
-        <v>43741.64</v>
+        <v>43741.66</v>
       </c>
     </row>
     <row r="423">
@@ -14526,7 +14526,7 @@
         <v>31</v>
       </c>
       <c r="G424" s="7" t="n">
-        <v>42345.66</v>
+        <v>42345.67</v>
       </c>
     </row>
     <row r="425">
@@ -14588,7 +14588,7 @@
         <v>31</v>
       </c>
       <c r="G426" s="7" t="n">
-        <v>41729.63</v>
+        <v>41729.64</v>
       </c>
     </row>
     <row r="427">
@@ -14621,7 +14621,7 @@
         <v>31</v>
       </c>
       <c r="G427" s="7" t="n">
-        <v>39961.16</v>
+        <v>39961.17</v>
       </c>
     </row>
     <row r="428">
@@ -14654,7 +14654,7 @@
         <v>31</v>
       </c>
       <c r="G428" s="7" t="n">
-        <v>39538.68</v>
+        <v>39538.67</v>
       </c>
     </row>
     <row r="429">
@@ -14753,7 +14753,7 @@
         <v>31</v>
       </c>
       <c r="G431" s="7" t="n">
-        <v>36982.54</v>
+        <v>36982.56</v>
       </c>
     </row>
     <row r="432">
@@ -14786,7 +14786,7 @@
         <v>31</v>
       </c>
       <c r="G432" s="7" t="n">
-        <v>36518.09</v>
+        <v>36518.08</v>
       </c>
     </row>
     <row r="433">
@@ -14852,7 +14852,7 @@
         <v>31</v>
       </c>
       <c r="G434" s="7" t="n">
-        <v>34841.02</v>
+        <v>34841.04</v>
       </c>
     </row>
     <row r="435">
@@ -14918,7 +14918,7 @@
         <v>31</v>
       </c>
       <c r="G436" s="7" t="n">
-        <v>33869.58</v>
+        <v>33869.57</v>
       </c>
     </row>
     <row r="437">
@@ -15017,7 +15017,7 @@
         <v>31</v>
       </c>
       <c r="G439" s="7" t="n">
-        <v>33222.77</v>
+        <v>33222.8</v>
       </c>
     </row>
     <row r="440">
@@ -15083,7 +15083,7 @@
         <v>31</v>
       </c>
       <c r="G441" s="7" t="n">
-        <v>31098.94</v>
+        <v>31098.95</v>
       </c>
     </row>
     <row r="442">
@@ -15149,7 +15149,7 @@
         <v>31</v>
       </c>
       <c r="G443" s="7" t="n">
-        <v>29392.28</v>
+        <v>29392.27</v>
       </c>
     </row>
     <row r="444">
@@ -15215,7 +15215,7 @@
         <v>31</v>
       </c>
       <c r="G445" s="7" t="n">
-        <v>28670.93</v>
+        <v>28670.95</v>
       </c>
     </row>
     <row r="446">
@@ -15248,7 +15248,7 @@
         <v>31</v>
       </c>
       <c r="G446" s="7" t="n">
-        <v>28066.07</v>
+        <v>28066.05</v>
       </c>
     </row>
     <row r="447">
@@ -15413,7 +15413,7 @@
         <v>31</v>
       </c>
       <c r="G451" s="7" t="n">
-        <v>26931.94</v>
+        <v>26931.96</v>
       </c>
     </row>
     <row r="452">
@@ -15512,7 +15512,7 @@
         <v>31</v>
       </c>
       <c r="G454" s="7" t="n">
-        <v>26376.47</v>
+        <v>26376.45</v>
       </c>
     </row>
     <row r="455">
@@ -15541,7 +15541,7 @@
         <v>31</v>
       </c>
       <c r="G455" s="7" t="n">
-        <v>26356.83</v>
+        <v>26356.82</v>
       </c>
     </row>
     <row r="456">
@@ -15673,7 +15673,7 @@
         <v>31</v>
       </c>
       <c r="G459" s="7" t="n">
-        <v>24820.25</v>
+        <v>24820.24</v>
       </c>
     </row>
     <row r="460">
@@ -15863,7 +15863,7 @@
         <v>31</v>
       </c>
       <c r="G465" s="7" t="n">
-        <v>23970.65</v>
+        <v>23970.67</v>
       </c>
     </row>
     <row r="466">
@@ -15958,7 +15958,7 @@
         <v>31</v>
       </c>
       <c r="G468" s="7" t="n">
-        <v>23485.64</v>
+        <v>23485.62</v>
       </c>
     </row>
     <row r="469">
@@ -15987,7 +15987,7 @@
         <v>31</v>
       </c>
       <c r="G469" s="7" t="n">
-        <v>23255.13</v>
+        <v>23255.11</v>
       </c>
     </row>
     <row r="470">
@@ -16053,7 +16053,7 @@
         <v>31</v>
       </c>
       <c r="G471" s="7" t="n">
-        <v>22332.15</v>
+        <v>22332.16</v>
       </c>
     </row>
     <row r="472">
@@ -16185,7 +16185,7 @@
         <v>31</v>
       </c>
       <c r="G475" s="7" t="n">
-        <v>19006.77</v>
+        <v>19006.79</v>
       </c>
     </row>
     <row r="476">
@@ -16218,7 +16218,7 @@
         <v>31</v>
       </c>
       <c r="G476" s="7" t="n">
-        <v>18937.51</v>
+        <v>18937.5</v>
       </c>
     </row>
     <row r="477">
@@ -16416,7 +16416,7 @@
         <v>31</v>
       </c>
       <c r="G482" s="7" t="n">
-        <v>17331.57</v>
+        <v>17331.59</v>
       </c>
     </row>
     <row r="483">
@@ -16482,7 +16482,7 @@
         <v>31</v>
       </c>
       <c r="G484" s="7" t="n">
-        <v>16622.73</v>
+        <v>16622.7</v>
       </c>
     </row>
     <row r="485">
@@ -16581,7 +16581,7 @@
         <v>31</v>
       </c>
       <c r="G487" s="7" t="n">
-        <v>15857.11</v>
+        <v>15857.09</v>
       </c>
     </row>
     <row r="488">
@@ -16779,7 +16779,7 @@
         <v>31</v>
       </c>
       <c r="G493" s="7" t="n">
-        <v>14028.11</v>
+        <v>14028.1</v>
       </c>
     </row>
     <row r="494">
@@ -17076,7 +17076,7 @@
         <v>31</v>
       </c>
       <c r="G502" s="7" t="n">
-        <v>12057.9</v>
+        <v>12057.88</v>
       </c>
     </row>
     <row r="503">
@@ -17241,7 +17241,7 @@
         <v>31</v>
       </c>
       <c r="G507" s="7" t="n">
-        <v>11087.03</v>
+        <v>11087.04</v>
       </c>
     </row>
     <row r="508">
@@ -17637,7 +17637,7 @@
         <v>31</v>
       </c>
       <c r="G519" s="7" t="n">
-        <v>9501.43</v>
+        <v>9501.41</v>
       </c>
     </row>
     <row r="520">
@@ -17670,7 +17670,7 @@
         <v>31</v>
       </c>
       <c r="G520" s="7" t="n">
-        <v>9352.91</v>
+        <v>9352.93</v>
       </c>
     </row>
     <row r="521">
@@ -17769,7 +17769,7 @@
         <v>31</v>
       </c>
       <c r="G523" s="7" t="n">
-        <v>8609.620000000001</v>
+        <v>8609.629999999999</v>
       </c>
     </row>
     <row r="524">
@@ -17802,7 +17802,7 @@
         <v>31</v>
       </c>
       <c r="G524" s="7" t="n">
-        <v>8360.57</v>
+        <v>8360.559999999999</v>
       </c>
     </row>
     <row r="525">
@@ -17835,7 +17835,7 @@
         <v>31</v>
       </c>
       <c r="G525" s="7" t="n">
-        <v>8302.610000000001</v>
+        <v>8302.629999999999</v>
       </c>
     </row>
     <row r="526">
@@ -18029,7 +18029,7 @@
         <v>31</v>
       </c>
       <c r="G531" s="7" t="n">
-        <v>7458.79</v>
+        <v>7458.78</v>
       </c>
     </row>
     <row r="532">
@@ -18095,7 +18095,7 @@
         <v>31</v>
       </c>
       <c r="G533" s="7" t="n">
-        <v>7328.59</v>
+        <v>7328.58</v>
       </c>
     </row>
     <row r="534">
@@ -18289,7 +18289,7 @@
         <v>31</v>
       </c>
       <c r="G539" s="7" t="n">
-        <v>6820.63</v>
+        <v>6820.62</v>
       </c>
     </row>
     <row r="540">
@@ -18549,7 +18549,7 @@
         <v>31</v>
       </c>
       <c r="G547" s="7" t="n">
-        <v>5573.85</v>
+        <v>5573.87</v>
       </c>
     </row>
     <row r="548">
@@ -19230,7 +19230,7 @@
         <v>31</v>
       </c>
       <c r="G568" s="7" t="n">
-        <v>3451.98</v>
+        <v>3451.97</v>
       </c>
     </row>
     <row r="569">
@@ -19263,7 +19263,7 @@
         <v>31</v>
       </c>
       <c r="G569" s="7" t="n">
-        <v>3447.27</v>
+        <v>3447.28</v>
       </c>
     </row>
     <row r="570">
@@ -19325,7 +19325,7 @@
         <v>31</v>
       </c>
       <c r="G571" s="7" t="n">
-        <v>3356.93</v>
+        <v>3356.92</v>
       </c>
     </row>
     <row r="572">
@@ -19391,7 +19391,7 @@
         <v>31</v>
       </c>
       <c r="G573" s="7" t="n">
-        <v>3139.69</v>
+        <v>3139.72</v>
       </c>
     </row>
     <row r="574">
@@ -19548,7 +19548,7 @@
         <v>31</v>
       </c>
       <c r="G578" s="7" t="n">
-        <v>2919.73</v>
+        <v>2919.74</v>
       </c>
     </row>
     <row r="579">
@@ -19738,7 +19738,7 @@
         <v>31</v>
       </c>
       <c r="G584" s="7" t="n">
-        <v>2712.77</v>
+        <v>2712.76</v>
       </c>
     </row>
     <row r="585">
@@ -19837,7 +19837,7 @@
         <v>31</v>
       </c>
       <c r="G587" s="7" t="n">
-        <v>2585.01</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="588">
@@ -19932,7 +19932,7 @@
         <v>31</v>
       </c>
       <c r="G590" s="7" t="n">
-        <v>2375.35</v>
+        <v>2375.34</v>
       </c>
     </row>
     <row r="591">
@@ -19998,7 +19998,7 @@
         <v>31</v>
       </c>
       <c r="G592" s="7" t="n">
-        <v>2270.02</v>
+        <v>2270.03</v>
       </c>
     </row>
     <row r="593">
@@ -20126,7 +20126,7 @@
         <v>31</v>
       </c>
       <c r="G596" s="7" t="n">
-        <v>2127.24</v>
+        <v>2127.26</v>
       </c>
     </row>
     <row r="597">
@@ -20791,7 +20791,7 @@
         <v>31</v>
       </c>
       <c r="G617" s="7" t="n">
-        <v>1269.49</v>
+        <v>1269.5</v>
       </c>
     </row>
     <row r="618">
@@ -20915,7 +20915,7 @@
         <v>31</v>
       </c>
       <c r="G621" s="7" t="n">
-        <v>908.71</v>
+        <v>908.74</v>
       </c>
     </row>
     <row r="622">
@@ -20981,7 +20981,7 @@
         <v>31</v>
       </c>
       <c r="G623" s="7" t="n">
-        <v>883.5</v>
+        <v>883.52</v>
       </c>
     </row>
     <row r="624">
@@ -22522,7 +22522,7 @@
         <v>31</v>
       </c>
       <c r="G672" s="7" t="n">
-        <v>222.51</v>
+        <v>222.5</v>
       </c>
     </row>
     <row r="673">

--- a/NBS FINAL delivery/03_Excel_Deliveries/8_Artist_Population_Frame.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/8_Artist_Population_Frame.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Population_Frame" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Residency_Adjudication'!$A$1:$G$735</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Residency_Adjudication'!$A$1:$G$735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Residency_Adjudication'!$A$1:$G$734</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Residency_Adjudication'!$A$1:$G$734</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Population_Frame'!$A$1:$L$856</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Population_Frame'!$A$1:$L$856</definedName>
   </definedNames>
@@ -515,7 +515,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31T23:48:51.976270+00:00</t>
+          <t>2026-09-01T00:10:26.191025+00:00</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G735"/>
+  <dimension ref="A1:G734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5925,7 +5925,7 @@
         <v>31</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>604469.85</v>
+        <v>602295.53</v>
       </c>
     </row>
     <row r="164">
@@ -23871,142 +23871,146 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Odunsi</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr"/>
+          <t>Adé Bantu</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>provider holds no country for this artist</t>
+          <t>provider registers the artist in Nigeria</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F716" s="6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G716" s="7" t="n">
-        <v>7.99</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Adé Bantu</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
+          <t>Msquare</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr"/>
       <c r="C717" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>provider registers the artist in Nigeria</t>
+          <t>provider holds no country for this artist</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F717" s="6" t="n">
         <v>20</v>
       </c>
       <c r="G717" s="7" t="n">
-        <v>7.33</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Msquare</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr"/>
+          <t>IllRymz</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>provider holds no country for this artist</t>
+          <t>provider registers the artist in Nigeria</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F718" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G718" s="7" t="n">
-        <v>6.95</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>IllRymz</t>
-        </is>
-      </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
+          <t>Yusuf Olatunji</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>provider registers the artist in Nigeria</t>
+          <t>provider holds no country for this artist</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F719" s="6" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G719" s="7" t="n">
-        <v>6.23</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Yusuf Olatunji</t>
-        </is>
-      </c>
-      <c r="B720" t="inlineStr"/>
+          <t>Eso Dike</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>diaspora_candidate</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>provider holds no country for this artist</t>
+          <t>provider registers the artist in US</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -24015,31 +24019,27 @@
         </is>
       </c>
       <c r="F720" s="6" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G720" s="7" t="n">
-        <v>6.11</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Eso Dike</t>
-        </is>
-      </c>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+          <t>Ayinla Kollington</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr"/>
       <c r="C721" t="inlineStr">
         <is>
-          <t>diaspora_candidate</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>provider registers the artist in US</t>
+          <t>provider holds no country for this artist</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -24048,16 +24048,16 @@
         </is>
       </c>
       <c r="F721" s="6" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G721" s="7" t="n">
-        <v>5.87</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Ayinla Kollington</t>
+          <t>Michael Ekeghasi</t>
         </is>
       </c>
       <c r="B722" t="inlineStr"/>
@@ -24077,16 +24077,16 @@
         </is>
       </c>
       <c r="F722" s="6" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G722" s="7" t="n">
-        <v>4.47</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Michael Ekeghasi</t>
+          <t>Kunle Ajayi</t>
         </is>
       </c>
       <c r="B723" t="inlineStr"/>
@@ -24106,16 +24106,16 @@
         </is>
       </c>
       <c r="F723" s="6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G723" s="7" t="n">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Kunle Ajayi</t>
+          <t>Taye Currency</t>
         </is>
       </c>
       <c r="B724" t="inlineStr"/>
@@ -24135,16 +24135,16 @@
         </is>
       </c>
       <c r="F724" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G724" s="7" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Taye Currency</t>
+          <t>DJ Bally</t>
         </is>
       </c>
       <c r="B725" t="inlineStr"/>
@@ -24164,16 +24164,16 @@
         </is>
       </c>
       <c r="F725" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G725" s="7" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DJ Bally</t>
+          <t>Taye Olusola</t>
         </is>
       </c>
       <c r="B726" t="inlineStr"/>
@@ -24193,16 +24193,16 @@
         </is>
       </c>
       <c r="F726" s="6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G726" s="7" t="n">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Taye Olusola</t>
+          <t>JJC Skillz</t>
         </is>
       </c>
       <c r="B727" t="inlineStr"/>
@@ -24222,16 +24222,16 @@
         </is>
       </c>
       <c r="F727" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G727" s="7" t="n">
-        <v>1.28</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>JJC Skillz</t>
+          <t>Bhadboy OML</t>
         </is>
       </c>
       <c r="B728" t="inlineStr"/>
@@ -24251,69 +24251,69 @@
         </is>
       </c>
       <c r="F728" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G728" s="7" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Bhadboy OML</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr"/>
+          <t>Dede Mabiaku</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>provider holds no country for this artist</t>
+          <t>provider registers the artist in Nigeria</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F729" s="6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G729" s="7" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Dede Mabiaku</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
+          <t>Oluwatobi Oyero</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr"/>
       <c r="C730" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>provider registers the artist in Nigeria</t>
+          <t>provider holds no country for this artist</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F730" s="6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G730" s="7" t="n">
         <v>0.37</v>
@@ -24322,7 +24322,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Oluwatobi Oyero</t>
+          <t>Hurlarstringz</t>
         </is>
       </c>
       <c r="B731" t="inlineStr"/>
@@ -24342,16 +24342,16 @@
         </is>
       </c>
       <c r="F731" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G731" s="7" t="n">
-        <v>0.37</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Hurlarstringz</t>
+          <t>Naziru Sarkin Waka</t>
         </is>
       </c>
       <c r="B732" t="inlineStr"/>
@@ -24371,16 +24371,16 @@
         </is>
       </c>
       <c r="F732" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G732" s="7" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Naziru Sarkin Waka</t>
+          <t>Al’ameen</t>
         </is>
       </c>
       <c r="B733" t="inlineStr"/>
@@ -24400,16 +24400,16 @@
         </is>
       </c>
       <c r="F733" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G733" s="7" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>Al’ameen</t>
+          <t>Salawa Abeni</t>
         </is>
       </c>
       <c r="B734" t="inlineStr"/>
@@ -24432,40 +24432,11 @@
         <v>1</v>
       </c>
       <c r="G734" s="7" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>Salawa Abeni</t>
-        </is>
-      </c>
-      <c r="B735" t="inlineStr"/>
-      <c r="C735" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="D735" t="inlineStr">
-        <is>
-          <t>provider holds no country for this artist</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F735" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G735" s="7" t="n">
         <v>0.02</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G735"/>
+  <autoFilter ref="A1:G734"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/NBS FINAL delivery/03_Excel_Deliveries/8_Artist_Population_Frame.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/8_Artist_Population_Frame.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:10:26.191025+00:00</t>
+          <t>2026-09-01T00:38:12.797681+00:00</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
         <v>31</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>7216616.45</v>
+        <v>7170813.84</v>
       </c>
     </row>
     <row r="21">
@@ -5925,7 +5925,7 @@
         <v>31</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>602295.53</v>
+        <v>604469.85</v>
       </c>
     </row>
     <row r="164">
